--- a/data/key對照表.xlsx
+++ b/data/key對照表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK3"/>
+  <dimension ref="A1:AK10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -877,6 +877,993 @@
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Tang 在測試ㄉ</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>直白雙離子高速吹風機S1(白)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>高速BLDC正負離子吹風機-小甜筒-兩色可選(S1)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>台灣金點設計獎</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>速乾不耗時
+超羽量級378g
+2.4億正負離子</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>XXXXXX</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1234567891111</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>6971016545882</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ZHIBAI 直白</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>顏⾊</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>紅</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>36.3</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>18.8</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>應稅</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>4990</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2980</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>非廢四機回收商品</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>常溫</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>中國</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Tang 在測試ㄉ</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>直白雙離子高速吹風機S1(白)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>高速BLDC正負離子吹風機-小甜筒-兩色可選(S1)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>台灣金點設計獎</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>速乾不耗時
+超羽量級378g
+2.4億正負離子</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>XXXXXX</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1234567891112</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>6971016545882</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ZHIBAI 直白</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>顏⾊</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>橙</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>36.3</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>18.8</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>應稅</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>4990</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>2980</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>非廢四機回收商品</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>常溫</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>中國</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Tang 在測試ㄉ</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>直白雙離子高速吹風機S1(白)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>高速BLDC正負離子吹風機-小甜筒-兩色可選(S1)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>台灣金點設計獎</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>速乾不耗時
+超羽量級378g
+2.4億正負離子</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>XXXXXX</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1234567891113</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>6971016545882</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ZHIBAI 直白</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>顏⾊</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>黃</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>36.3</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>18.8</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>應稅</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>4990</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>2980</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>非廢四機回收商品</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>常溫</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>中國</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Tang 在測試ㄉ</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>直白雙離子高速吹風機S1(白)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>高速BLDC正負離子吹風機-小甜筒-兩色可選(S1)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>台灣金點設計獎</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>速乾不耗時
+超羽量級378g
+2.4億正負離子</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>XXXXXX</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1234567891114</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>6971016545882</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ZHIBAI 直白</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>顏⾊</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>綠</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>36.3</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>18.8</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>應稅</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>4990</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>2980</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>非廢四機回收商品</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>常溫</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>中國</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Tang 在測試ㄉ</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>直白雙離子高速吹風機S1(白)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>高速BLDC正負離子吹風機-小甜筒-兩色可選(S1)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>台灣金點設計獎</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>速乾不耗時
+超羽量級378g
+2.4億正負離子</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>XXXXXX</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1234567891115</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>6971016545882</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ZHIBAI 直白</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>顏⾊</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>藍</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>36.3</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>18.8</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>應稅</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>4990</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>2980</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>非廢四機回收商品</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>常溫</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>中國</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Tang 在測試ㄉ</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>直白雙離子高速吹風機S1(白)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>高速BLDC正負離子吹風機-小甜筒-兩色可選(S1)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>台灣金點設計獎</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>速乾不耗時
+超羽量級378g
+2.4億正負離子</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>XXXXXX</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1234567891116</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>6971016545882</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ZHIBAI 直白</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>顏⾊</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>黑</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>36.3</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>18.8</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>應稅</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>4990</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>2980</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>非廢四機回收商品</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>常溫</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>中國</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Tang 在測試ㄉ</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>直白雙離子高速吹風機S1(白)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>高速BLDC正負離子吹風機-小甜筒-兩色可選(S1)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>台灣金點設計獎</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>速乾不耗時
+超羽量級378g
+2.4億正負離子</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>XXXXXX</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1234567891117</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>6971016545882</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ZHIBAI 直白</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>顏⾊</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>紫</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>36.3</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>18.8</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>應稅</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>4990</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>2980</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>非廢四機回收商品</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>常溫</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>中國</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/key對照表.xlsx
+++ b/data/key對照表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK3"/>
+  <dimension ref="A1:AM3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -602,6 +602,16 @@
           <t>warranty_days</t>
         </is>
       </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>BSMI</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>NCC</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr"/>
@@ -701,7 +711,11 @@
           <t>100</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
           <t>TRUE</t>
@@ -736,9 +750,15 @@
           <t>中國</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
@@ -838,7 +858,11 @@
           <t>100</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
           <t>TRUE</t>
@@ -873,9 +897,15 @@
           <t>中國</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
